--- a/public/sap-reporting/expansion-150-downloads/EXT-SD08-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-SD08-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R054e8763b52c4529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Ref16072ae0dc48a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R12a98bfd28ef444b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rad99f614b41f456d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R0a5c55b4d3a24c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R846464c85d734b55"/>
   </x:sheets>
 </x:workbook>
 </file>
